--- a/data/trans_orig/P21D_5_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262773</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296259</t>
+          <t>296213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561242</t>
+          <t>561165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>440462</t>
+          <t>440757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446162</t>
+          <t>446192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1098188</t>
+          <t>1098859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1104761</t>
+          <t>1104640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,62 +1451,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5024</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5064</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>325343</t>
+          <t>325795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327533</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654434</t>
+          <t>654474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>402033</t>
+          <t>401877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>510439</t>
+          <t>510347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>516394</t>
+          <t>516249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>915012</t>
+          <t>915305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>923235</t>
+          <t>923342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1654702</t>
+          <t>1654386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1662825</t>
+          <t>1662916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1580255</t>
+          <t>1580377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1589150</t>
+          <t>1589055</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3240081</t>
+          <t>3239555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3251006</t>
+          <t>3250484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_5_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>265906</t>
+          <t>287463</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262513</t>
+          <t>283756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>298551</t>
+          <t>322861</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296213</t>
+          <t>320030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>564456</t>
+          <t>610324</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561165</t>
+          <t>607170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>444455</t>
+          <t>499916</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>440757</t>
+          <t>495528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446192</t>
+          <t>502106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1102845</t>
+          <t>970124</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1098859</t>
+          <t>965899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1104640</t>
+          <t>972315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>329670</t>
+          <t>374433</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>325795</t>
+          <t>370232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330674</t>
+          <t>375428</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>658494</t>
+          <t>752485</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654474</t>
+          <t>747570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659498</t>
+          <t>753480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>330674</t>
+          <t>375428</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330674</t>
+          <t>375428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330674</t>
+          <t>375428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>659498</t>
+          <t>753480</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>659498</t>
+          <t>753480</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>659498</t>
+          <t>753480</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>406269</t>
+          <t>431628</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>401877</t>
+          <t>427495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>514266</t>
+          <t>486865</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>510347</t>
+          <t>482278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>516249</t>
+          <t>488804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>920534</t>
+          <t>918494</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>915305</t>
+          <t>912631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>923342</t>
+          <t>921233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,67 +2097,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -2210,69 +2210,69 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1660233</t>
+          <t>1563733</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1654386</t>
+          <t>1558544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1662916</t>
+          <t>1566129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2362</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1687695</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1681826</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1691005</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2362</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1586096</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1580377</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1589055</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>3817</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3246329</t>
+          <t>3251428</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3239555</t>
+          <t>3244752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3250484</t>
+          <t>3255790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
